--- a/data/rokudo_rows.xlsx
+++ b/data/rokudo_rows.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="rokudo rows" sheetId="1" r:id="rId1"/>
+    <sheet name="SKUs append" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -512,7 +512,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SKU0090</v>
+        <v>SKU0278</v>
       </c>
       <c r="B2" t="str">
         <v>tire</v>
@@ -545,7 +545,7 @@
         <v>8</v>
       </c>
       <c r="L2" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -592,7 +592,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SKU0091</v>
+        <v>SKU0279</v>
       </c>
       <c r="B3" t="str">
         <v>tire</v>
@@ -625,7 +625,7 @@
         <v>8</v>
       </c>
       <c r="L3" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -672,7 +672,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SKU0092</v>
+        <v>SKU0280</v>
       </c>
       <c r="B4" t="str">
         <v>tire</v>
@@ -705,7 +705,7 @@
         <v>8</v>
       </c>
       <c r="L4" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -752,7 +752,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SKU0093</v>
+        <v>SKU0281</v>
       </c>
       <c r="B5" t="str">
         <v>tire</v>
@@ -785,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="L5" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -832,7 +832,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SKU0094</v>
+        <v>SKU0282</v>
       </c>
       <c r="B6" t="str">
         <v>tire</v>
@@ -865,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -912,7 +912,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SKU0095</v>
+        <v>SKU0283</v>
       </c>
       <c r="B7" t="str">
         <v>tire</v>
@@ -945,7 +945,7 @@
         <v>8</v>
       </c>
       <c r="L7" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -992,7 +992,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SKU0096</v>
+        <v>SKU0284</v>
       </c>
       <c r="B8" t="str">
         <v>tire</v>
@@ -1025,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="L8" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SKU0097</v>
+        <v>SKU0285</v>
       </c>
       <c r="B9" t="str">
         <v>tire</v>
@@ -1105,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="L9" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SKU0098</v>
+        <v>SKU0286</v>
       </c>
       <c r="B10" t="str">
         <v>tire</v>
@@ -1185,7 +1185,7 @@
         <v>8</v>
       </c>
       <c r="L10" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SKU0099</v>
+        <v>SKU0287</v>
       </c>
       <c r="B11" t="str">
         <v>tire</v>
@@ -1265,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="L11" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SKU0100</v>
+        <v>SKU0288</v>
       </c>
       <c r="B12" t="str">
         <v>tire</v>
@@ -1345,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="L12" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SKU0101</v>
+        <v>SKU0289</v>
       </c>
       <c r="B13" t="str">
         <v>tire</v>
@@ -1425,7 +1425,7 @@
         <v>8</v>
       </c>
       <c r="L13" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -1472,7 +1472,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SKU0102</v>
+        <v>SKU0290</v>
       </c>
       <c r="B14" t="str">
         <v>tire</v>
@@ -1505,7 +1505,7 @@
         <v>8</v>
       </c>
       <c r="L14" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SKU0103</v>
+        <v>SKU0291</v>
       </c>
       <c r="B15" t="str">
         <v>tire</v>
@@ -1585,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="L15" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SKU0104</v>
+        <v>SKU0292</v>
       </c>
       <c r="B16" t="str">
         <v>tire</v>
@@ -1665,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="L16" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SKU0105</v>
+        <v>SKU0293</v>
       </c>
       <c r="B17" t="str">
         <v>tire</v>
@@ -1745,7 +1745,7 @@
         <v>8</v>
       </c>
       <c r="L17" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SKU0106</v>
+        <v>SKU0294</v>
       </c>
       <c r="B18" t="str">
         <v>tire</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="L18" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SKU0107</v>
+        <v>SKU0295</v>
       </c>
       <c r="B19" t="str">
         <v>tire</v>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="L19" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SKU0108</v>
+        <v>SKU0296</v>
       </c>
       <c r="B20" t="str">
         <v>tire</v>
@@ -1985,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="L20" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SKU0109</v>
+        <v>SKU0297</v>
       </c>
       <c r="B21" t="str">
         <v>tire</v>
@@ -2065,7 +2065,7 @@
         <v>8</v>
       </c>
       <c r="L21" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SKU0110</v>
+        <v>SKU0298</v>
       </c>
       <c r="B22" t="str">
         <v>tire</v>
@@ -2145,7 +2145,7 @@
         <v>8</v>
       </c>
       <c r="L22" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SKU0111</v>
+        <v>SKU0299</v>
       </c>
       <c r="B23" t="str">
         <v>tire</v>
@@ -2225,7 +2225,7 @@
         <v>8</v>
       </c>
       <c r="L23" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SKU0112</v>
+        <v>SKU0300</v>
       </c>
       <c r="B24" t="str">
         <v>tire</v>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="L24" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SKU0113</v>
+        <v>SKU0301</v>
       </c>
       <c r="B25" t="str">
         <v>tire</v>
@@ -2385,7 +2385,7 @@
         <v>8</v>
       </c>
       <c r="L25" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SKU0114</v>
+        <v>SKU0302</v>
       </c>
       <c r="B26" t="str">
         <v>tire</v>
@@ -2465,7 +2465,7 @@
         <v>8</v>
       </c>
       <c r="L26" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -2512,7 +2512,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SKU0115</v>
+        <v>SKU0303</v>
       </c>
       <c r="B27" t="str">
         <v>tire</v>
@@ -2545,7 +2545,7 @@
         <v>8</v>
       </c>
       <c r="L27" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -2592,7 +2592,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SKU0116</v>
+        <v>SKU0304</v>
       </c>
       <c r="B28" t="str">
         <v>tire</v>
@@ -2625,7 +2625,7 @@
         <v>8</v>
       </c>
       <c r="L28" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SKU0117</v>
+        <v>SKU0305</v>
       </c>
       <c r="B29" t="str">
         <v>tire</v>
@@ -2705,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="L29" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SKU0118</v>
+        <v>SKU0306</v>
       </c>
       <c r="B30" t="str">
         <v>tire</v>
@@ -2785,7 +2785,7 @@
         <v>8</v>
       </c>
       <c r="L30" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SKU0119</v>
+        <v>SKU0307</v>
       </c>
       <c r="B31" t="str">
         <v>tire</v>
@@ -2865,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="L31" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SKU0120</v>
+        <v>SKU0308</v>
       </c>
       <c r="B32" t="str">
         <v>tire</v>
@@ -2945,7 +2945,7 @@
         <v>8</v>
       </c>
       <c r="L32" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SKU0121</v>
+        <v>SKU0309</v>
       </c>
       <c r="B33" t="str">
         <v>tire</v>
@@ -3025,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="L33" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SKU0122</v>
+        <v>SKU0310</v>
       </c>
       <c r="B34" t="str">
         <v>tire</v>
@@ -3105,7 +3105,7 @@
         <v>8</v>
       </c>
       <c r="L34" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SKU0123</v>
+        <v>SKU0311</v>
       </c>
       <c r="B35" t="str">
         <v>tire</v>
@@ -3185,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="L35" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SKU0124</v>
+        <v>SKU0312</v>
       </c>
       <c r="B36" t="str">
         <v>tire</v>
@@ -3265,7 +3265,7 @@
         <v>8</v>
       </c>
       <c r="L36" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SKU0125</v>
+        <v>SKU0313</v>
       </c>
       <c r="B37" t="str">
         <v>tire</v>
@@ -3345,7 +3345,7 @@
         <v>8</v>
       </c>
       <c r="L37" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -3392,7 +3392,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SKU0126</v>
+        <v>SKU0314</v>
       </c>
       <c r="B38" t="str">
         <v>tire</v>
@@ -3425,7 +3425,7 @@
         <v>8</v>
       </c>
       <c r="L38" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SKU0127</v>
+        <v>SKU0315</v>
       </c>
       <c r="B39" t="str">
         <v>tire</v>
@@ -3505,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="L39" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SKU0128</v>
+        <v>SKU0316</v>
       </c>
       <c r="B40" t="str">
         <v>tire</v>
@@ -3585,7 +3585,7 @@
         <v>8</v>
       </c>
       <c r="L40" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -3632,7 +3632,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SKU0129</v>
+        <v>SKU0317</v>
       </c>
       <c r="B41" t="str">
         <v>tire</v>
@@ -3665,7 +3665,7 @@
         <v>8</v>
       </c>
       <c r="L41" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -3712,7 +3712,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SKU0130</v>
+        <v>SKU0318</v>
       </c>
       <c r="B42" t="str">
         <v>tire</v>
@@ -3745,7 +3745,7 @@
         <v>8</v>
       </c>
       <c r="L42" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SKU0131</v>
+        <v>SKU0319</v>
       </c>
       <c r="B43" t="str">
         <v>tire</v>
@@ -3825,7 +3825,7 @@
         <v>8</v>
       </c>
       <c r="L43" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -3872,7 +3872,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SKU0132</v>
+        <v>SKU0320</v>
       </c>
       <c r="B44" t="str">
         <v>tire</v>
@@ -3905,7 +3905,7 @@
         <v>8</v>
       </c>
       <c r="L44" t="str">
-        <v>WL; Sentury pricelist 2026</v>
+        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SKU0133</v>
+        <v>SKU0321</v>
       </c>
       <c r="B45" t="str">
         <v>tire</v>
@@ -3985,7 +3985,7 @@
         <v>8</v>
       </c>
       <c r="L45" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -4032,7 +4032,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SKU0134</v>
+        <v>SKU0322</v>
       </c>
       <c r="B46" t="str">
         <v>tire</v>
@@ -4065,7 +4065,7 @@
         <v>8</v>
       </c>
       <c r="L46" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SKU0135</v>
+        <v>SKU0323</v>
       </c>
       <c r="B47" t="str">
         <v>tire</v>
@@ -4145,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="L47" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SKU0136</v>
+        <v>SKU0324</v>
       </c>
       <c r="B48" t="str">
         <v>tire</v>
@@ -4225,7 +4225,7 @@
         <v>8</v>
       </c>
       <c r="L48" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SKU0137</v>
+        <v>SKU0325</v>
       </c>
       <c r="B49" t="str">
         <v>tire</v>
@@ -4305,7 +4305,7 @@
         <v>8</v>
       </c>
       <c r="L49" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SKU0138</v>
+        <v>SKU0326</v>
       </c>
       <c r="B50" t="str">
         <v>tire</v>
@@ -4385,7 +4385,7 @@
         <v>8</v>
       </c>
       <c r="L50" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SKU0139</v>
+        <v>SKU0327</v>
       </c>
       <c r="B51" t="str">
         <v>tire</v>
@@ -4465,7 +4465,7 @@
         <v>8</v>
       </c>
       <c r="L51" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -4512,7 +4512,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SKU0140</v>
+        <v>SKU0328</v>
       </c>
       <c r="B52" t="str">
         <v>tire</v>
@@ -4545,7 +4545,7 @@
         <v>8</v>
       </c>
       <c r="L52" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -4592,7 +4592,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SKU0141</v>
+        <v>SKU0329</v>
       </c>
       <c r="B53" t="str">
         <v>tire</v>
@@ -4625,7 +4625,7 @@
         <v>8</v>
       </c>
       <c r="L53" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SKU0142</v>
+        <v>SKU0330</v>
       </c>
       <c r="B54" t="str">
         <v>tire</v>
@@ -4705,7 +4705,7 @@
         <v>8</v>
       </c>
       <c r="L54" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -4752,7 +4752,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SKU0143</v>
+        <v>SKU0331</v>
       </c>
       <c r="B55" t="str">
         <v>tire</v>
@@ -4785,7 +4785,7 @@
         <v>8</v>
       </c>
       <c r="L55" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -4832,7 +4832,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SKU0144</v>
+        <v>SKU0332</v>
       </c>
       <c r="B56" t="str">
         <v>tire</v>
@@ -4865,7 +4865,7 @@
         <v>8</v>
       </c>
       <c r="L56" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SKU0145</v>
+        <v>SKU0333</v>
       </c>
       <c r="B57" t="str">
         <v>tire</v>
@@ -4945,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="L57" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -4992,7 +4992,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SKU0146</v>
+        <v>SKU0334</v>
       </c>
       <c r="B58" t="str">
         <v>tire</v>
@@ -5025,7 +5025,7 @@
         <v>8</v>
       </c>
       <c r="L58" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -5072,7 +5072,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SKU0147</v>
+        <v>SKU0335</v>
       </c>
       <c r="B59" t="str">
         <v>tire</v>
@@ -5105,7 +5105,7 @@
         <v>8</v>
       </c>
       <c r="L59" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -5152,7 +5152,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SKU0148</v>
+        <v>SKU0336</v>
       </c>
       <c r="B60" t="str">
         <v>tire</v>
@@ -5185,7 +5185,7 @@
         <v>8</v>
       </c>
       <c r="L60" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SKU0149</v>
+        <v>SKU0337</v>
       </c>
       <c r="B61" t="str">
         <v>tire</v>
@@ -5265,7 +5265,7 @@
         <v>8</v>
       </c>
       <c r="L61" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -5312,7 +5312,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SKU0150</v>
+        <v>SKU0338</v>
       </c>
       <c r="B62" t="str">
         <v>tire</v>
@@ -5345,7 +5345,7 @@
         <v>8</v>
       </c>
       <c r="L62" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SKU0151</v>
+        <v>SKU0339</v>
       </c>
       <c r="B63" t="str">
         <v>tire</v>
@@ -5425,7 +5425,7 @@
         <v>8</v>
       </c>
       <c r="L63" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SKU0152</v>
+        <v>SKU0340</v>
       </c>
       <c r="B64" t="str">
         <v>tire</v>
@@ -5505,7 +5505,7 @@
         <v>8</v>
       </c>
       <c r="L64" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -5552,7 +5552,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SKU0153</v>
+        <v>SKU0341</v>
       </c>
       <c r="B65" t="str">
         <v>tire</v>
@@ -5585,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="L65" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -5632,7 +5632,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SKU0154</v>
+        <v>SKU0342</v>
       </c>
       <c r="B66" t="str">
         <v>tire</v>
@@ -5665,7 +5665,7 @@
         <v>8</v>
       </c>
       <c r="L66" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -5712,7 +5712,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SKU0155</v>
+        <v>SKU0343</v>
       </c>
       <c r="B67" t="str">
         <v>tire</v>
@@ -5745,7 +5745,7 @@
         <v>8</v>
       </c>
       <c r="L67" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SKU0156</v>
+        <v>SKU0344</v>
       </c>
       <c r="B68" t="str">
         <v>tire</v>
@@ -5825,7 +5825,7 @@
         <v>8</v>
       </c>
       <c r="L68" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -5872,7 +5872,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SKU0157</v>
+        <v>SKU0345</v>
       </c>
       <c r="B69" t="str">
         <v>tire</v>
@@ -5905,7 +5905,7 @@
         <v>8</v>
       </c>
       <c r="L69" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -5952,7 +5952,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SKU0158</v>
+        <v>SKU0346</v>
       </c>
       <c r="B70" t="str">
         <v>tire</v>
@@ -5985,7 +5985,7 @@
         <v>8</v>
       </c>
       <c r="L70" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -6032,7 +6032,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SKU0159</v>
+        <v>SKU0347</v>
       </c>
       <c r="B71" t="str">
         <v>tire</v>
@@ -6065,7 +6065,7 @@
         <v>8</v>
       </c>
       <c r="L71" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SKU0160</v>
+        <v>SKU0348</v>
       </c>
       <c r="B72" t="str">
         <v>tire</v>
@@ -6145,7 +6145,7 @@
         <v>8</v>
       </c>
       <c r="L72" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SKU0161</v>
+        <v>SKU0349</v>
       </c>
       <c r="B73" t="str">
         <v>tire</v>
@@ -6225,7 +6225,7 @@
         <v>8</v>
       </c>
       <c r="L73" t="str">
-        <v>Sentury pricelist 2026</v>
+        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
       </c>
       <c r="M73" t="str">
         <v/>

--- a/data/rokudo_rows.xlsx
+++ b/data/rokudo_rows.xlsx
@@ -545,7 +545,7 @@
         <v>8</v>
       </c>
       <c r="L2" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -625,7 +625,7 @@
         <v>8</v>
       </c>
       <c r="L3" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>8</v>
       </c>
       <c r="L4" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -785,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="L5" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -865,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -945,7 +945,7 @@
         <v>8</v>
       </c>
       <c r="L7" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -1025,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="L8" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -1105,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="L9" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -1185,7 +1185,7 @@
         <v>8</v>
       </c>
       <c r="L10" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -1265,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="L11" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -1345,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="L12" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -1425,7 +1425,7 @@
         <v>8</v>
       </c>
       <c r="L13" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -1505,7 +1505,7 @@
         <v>8</v>
       </c>
       <c r="L14" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="L15" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1665,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="L16" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1745,7 +1745,7 @@
         <v>8</v>
       </c>
       <c r="L17" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="L18" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="L19" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1985,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="L20" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -2065,7 +2065,7 @@
         <v>8</v>
       </c>
       <c r="L21" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -2145,7 +2145,7 @@
         <v>8</v>
       </c>
       <c r="L22" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>8</v>
       </c>
       <c r="L23" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="L24" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -2385,7 +2385,7 @@
         <v>8</v>
       </c>
       <c r="L25" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -2465,7 +2465,7 @@
         <v>8</v>
       </c>
       <c r="L26" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -2545,7 +2545,7 @@
         <v>8</v>
       </c>
       <c r="L27" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -2625,7 +2625,7 @@
         <v>8</v>
       </c>
       <c r="L28" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -2705,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="L29" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -2785,7 +2785,7 @@
         <v>8</v>
       </c>
       <c r="L30" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -2865,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="L31" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -2945,7 +2945,7 @@
         <v>8</v>
       </c>
       <c r="L32" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -3025,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="L33" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>8</v>
       </c>
       <c r="L34" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -3185,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="L35" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -3265,7 +3265,7 @@
         <v>8</v>
       </c>
       <c r="L36" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -3345,7 +3345,7 @@
         <v>8</v>
       </c>
       <c r="L37" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -3425,7 +3425,7 @@
         <v>8</v>
       </c>
       <c r="L38" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -3505,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="L39" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -3585,7 +3585,7 @@
         <v>8</v>
       </c>
       <c r="L40" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -3665,7 +3665,7 @@
         <v>8</v>
       </c>
       <c r="L41" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>8</v>
       </c>
       <c r="L42" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -3825,7 +3825,7 @@
         <v>8</v>
       </c>
       <c r="L43" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -3905,7 +3905,7 @@
         <v>8</v>
       </c>
       <c r="L44" t="str">
-        <v>WL; SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>WL; SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -3985,7 +3985,7 @@
         <v>8</v>
       </c>
       <c r="L45" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -4065,7 +4065,7 @@
         <v>8</v>
       </c>
       <c r="L46" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -4145,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="L47" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -4225,7 +4225,7 @@
         <v>8</v>
       </c>
       <c r="L48" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -4305,7 +4305,7 @@
         <v>8</v>
       </c>
       <c r="L49" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -4385,7 +4385,7 @@
         <v>8</v>
       </c>
       <c r="L50" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -4465,7 +4465,7 @@
         <v>8</v>
       </c>
       <c r="L51" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -4545,7 +4545,7 @@
         <v>8</v>
       </c>
       <c r="L52" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>8</v>
       </c>
       <c r="L53" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -4705,7 +4705,7 @@
         <v>8</v>
       </c>
       <c r="L54" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -4785,7 +4785,7 @@
         <v>8</v>
       </c>
       <c r="L55" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -4865,7 +4865,7 @@
         <v>8</v>
       </c>
       <c r="L56" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -4945,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="L57" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -5025,7 +5025,7 @@
         <v>8</v>
       </c>
       <c r="L58" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -5105,7 +5105,7 @@
         <v>8</v>
       </c>
       <c r="L59" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -5185,7 +5185,7 @@
         <v>8</v>
       </c>
       <c r="L60" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -5265,7 +5265,7 @@
         <v>8</v>
       </c>
       <c r="L61" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -5345,7 +5345,7 @@
         <v>8</v>
       </c>
       <c r="L62" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -5425,7 +5425,7 @@
         <v>8</v>
       </c>
       <c r="L63" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -5505,7 +5505,7 @@
         <v>8</v>
       </c>
       <c r="L64" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -5585,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="L65" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -5665,7 +5665,7 @@
         <v>8</v>
       </c>
       <c r="L66" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -5745,7 +5745,7 @@
         <v>8</v>
       </c>
       <c r="L67" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -5825,7 +5825,7 @@
         <v>8</v>
       </c>
       <c r="L68" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -5905,7 +5905,7 @@
         <v>8</v>
       </c>
       <c r="L69" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -5985,7 +5985,7 @@
         <v>8</v>
       </c>
       <c r="L70" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -6065,7 +6065,7 @@
         <v>8</v>
       </c>
       <c r="L71" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>8</v>
       </c>
       <c r="L72" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -6225,7 +6225,7 @@
         <v>8</v>
       </c>
       <c r="L73" t="str">
-        <v>SENTURY; New SKU 2026-09-04 - เพิ่มจากไฟล์ราคา ATV Sentury (ST_July)</v>
+        <v>SENTURY; ATV pricelist ST_July 2026</v>
       </c>
       <c r="M73" t="str">
         <v/>
